--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64969_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64969_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R85d0e4db8e734f79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbd170ea034f6462d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8114</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8691</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9286</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9443</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9526</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0528</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0038</x:v>
+        <x:v>      2.0213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0637</x:v>
+        <x:v>      1.9841</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0887</x:v>
+        <x:v>      2.0084</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1055</x:v>
+        <x:v>      2.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1016</x:v>
+        <x:v>      2.0210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2466</x:v>
+        <x:v>      2.1622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3365</x:v>
+        <x:v>      2.2498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3321</x:v>
+        <x:v>      2.2455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2641</x:v>
+        <x:v>      2.1792</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2821</x:v>
+        <x:v>      2.1968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3863</x:v>
+        <x:v>      2.2983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4334</x:v>
+        <x:v>      2.3443</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4713</x:v>
+        <x:v>      2.3812</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64969_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64969_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbd170ea034f6462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdb72a06cec434c9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8537</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9079</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9381</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8945</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9549</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3853</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4432</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3893</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5266</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4588</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5127</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4438</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5672</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8833</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8461</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7813</x:v>
+        <x:v>      1.9498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8114</x:v>
+        <x:v>      1.7979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7998</x:v>
+        <x:v>      1.8722</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8691</x:v>
+        <x:v>      1.8589</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9286</x:v>
+        <x:v>      1.9145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8979</x:v>
+        <x:v>      1.8840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9443</x:v>
+        <x:v>      1.9302</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9526</x:v>
+        <x:v>      1.9384</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0528</x:v>
+        <x:v>      2.0381</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0213</x:v>
+        <x:v>      2.0068</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9841</x:v>
+        <x:v>      1.9697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0084</x:v>
+        <x:v>      1.9940</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0248</x:v>
+        <x:v>      2.0103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0210</x:v>
+        <x:v>      2.0065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1622</x:v>
+        <x:v>      2.1470</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2498</x:v>
+        <x:v>      2.2341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2455</x:v>
+        <x:v>      2.2298</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1792</x:v>
+        <x:v>      2.1639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1968</x:v>
+        <x:v>      2.1814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2983</x:v>
+        <x:v>      2.2824</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3443</x:v>
+        <x:v>      2.3282</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3812</x:v>
+        <x:v>      2.3649</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.6660</x:v>
+        <x:v>     13.4335</x:v>
       </x:c>
     </x:row>
     <x:row>
